--- a/Excel-Finance/Finance-01/JLoka-Finance-01.xlsx
+++ b/Excel-Finance/Finance-01/JLoka-Finance-01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Tests\j-l-data-science-data-analytics\Excel-Finance\Finance-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358D0F7E-FE9A-4EA3-9CA1-6FE9BF7400B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC27389-8955-47E7-B5CF-3E8D23505E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1073,10 +1073,15 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1088,7 +1093,10 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1106,14 +1114,6 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1784,31 +1784,31 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>0.22518088577689821</c:v>
+                  <c:v>8.6915784118192341E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.6615126018486275E-2</c:v>
+                  <c:v>0.11100161243085194</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.8702354955083681</c:v>
+                  <c:v>0.66699718988218426</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.0926012166387684E-2</c:v>
+                  <c:v>0.24966708871427501</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>8.8551138159630782E-2</c:v>
+                  <c:v>0.87754600403962557</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.65332271221650706</c:v>
+                  <c:v>0.73911835572370288</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.79215614449270955</c:v>
+                  <c:v>0.85505503648803938</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.26667953215936857</c:v>
+                  <c:v>0.91854943503885156</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.99577635299164857</c:v>
+                  <c:v>0.53303090978041279</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1948,31 +1948,31 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>0.22356504089203866</c:v>
+                  <c:v>0.995673661150418</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.91547741076720424</c:v>
+                  <c:v>0.73304382628663689</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.5247083874135092E-2</c:v>
+                  <c:v>0.97227422532088059</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.57932526750454472</c:v>
+                  <c:v>0.94142684597969861</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.22884202106672469</c:v>
+                  <c:v>0.21421877494508046</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>7.4932411321734005E-2</c:v>
+                  <c:v>0.60395122269160229</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.15459971516135507</c:v>
+                  <c:v>9.4180672280433919E-3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.28533575202753148</c:v>
+                  <c:v>0.49813295330831853</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>5.9259036510320717E-3</c:v>
+                  <c:v>0.65868576205753238</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2112,31 +2112,31 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>0.55144837190485618</c:v>
+                  <c:v>0.52662624457069562</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.26848087893021488</c:v>
+                  <c:v>0.85318437891805488</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.22986145590904394</c:v>
+                  <c:v>0.32314197933022382</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.2486301162043244</c:v>
+                  <c:v>0.32787160268776661</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.84990396601828477</c:v>
+                  <c:v>0.83752860892351155</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.5123198633126851E-3</c:v>
+                  <c:v>0.48903074525455303</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>9.3087121970948261E-2</c:v>
+                  <c:v>0.77870766035609584</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.37420685227850292</c:v>
+                  <c:v>0.4116528241380023</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.96217109063538808</c:v>
+                  <c:v>0.64940899731822843</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4188,6 +4188,9 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{385DC015-9960-47FA-A637-6B66C3CB4FFA}" name="JLoka_Investors" displayName="JLoka_Investors" ref="B1:F9" totalsRowShown="0" dataDxfId="34" tableBorderDxfId="33">
   <autoFilter ref="B1:F9" xr:uid="{22AB70FF-96FA-4025-A517-8BDE3ECE5EBF}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:F9">
+    <sortCondition ref="B1:B9"/>
+  </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{0BE1A407-37E2-45E1-A4B9-6EE27C852CA8}" name="INVESTOR_ID" dataDxfId="32"/>
     <tableColumn id="2" xr3:uid="{F40E02B0-B4B8-4130-A683-00045FEF2BC6}" name="INVESTOR_NAME" dataDxfId="31"/>
@@ -4901,7 +4904,7 @@
       </c>
       <c r="D3" s="2">
         <f ca="1">RANDBETWEEN(250, 3200)</f>
-        <v>3198</v>
+        <v>2863</v>
       </c>
       <c r="E3" s="60">
         <f ca="1">RANDBETWEEN(0, 2)</f>
@@ -4912,7 +4915,7 @@
       </c>
       <c r="H3" s="2">
         <f ca="1">VLOOKUP($G3, Table1[], 3, FALSE)</f>
-        <v>3198</v>
+        <v>2863</v>
       </c>
       <c r="I3" s="2">
         <f ca="1">VLOOKUP($G3, Table1[], 4, FALSE)</f>
@@ -4928,7 +4931,7 @@
       </c>
       <c r="D4" s="2">
         <f t="shared" ref="D4:D12" ca="1" si="0">RANDBETWEEN(250, 3200)</f>
-        <v>2902</v>
+        <v>3174</v>
       </c>
       <c r="E4" s="60">
         <f t="shared" ref="E4:E12" ca="1" si="1">RANDBETWEEN(0, 2)</f>
@@ -4939,7 +4942,7 @@
       </c>
       <c r="H4" s="2">
         <f ca="1">VLOOKUP($G4, Table1[], 3, FALSE)</f>
-        <v>2902</v>
+        <v>3174</v>
       </c>
       <c r="I4" s="2">
         <f ca="1">VLOOKUP($G4, Table1[], 4, FALSE)</f>
@@ -4955,22 +4958,22 @@
       </c>
       <c r="D5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>2829</v>
+        <v>411</v>
       </c>
       <c r="E5" s="60">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" t="s">
         <v>79</v>
       </c>
       <c r="H5" s="2">
         <f ca="1">VLOOKUP($G5, Table1[], 3, FALSE)</f>
-        <v>1855</v>
+        <v>796</v>
       </c>
       <c r="I5" s="2">
         <f ca="1">VLOOKUP($G5, Table1[], 4, FALSE)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
@@ -4982,7 +4985,7 @@
       </c>
       <c r="D6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>1333</v>
+        <v>955</v>
       </c>
       <c r="E6" s="60">
         <f t="shared" ca="1" si="1"/>
@@ -4993,11 +4996,11 @@
       </c>
       <c r="H6" s="2">
         <f ca="1">VLOOKUP($G6, Table1[], 3, FALSE)</f>
-        <v>2607</v>
+        <v>1621</v>
       </c>
       <c r="I6" s="2">
         <f ca="1">VLOOKUP($G6, Table1[], 4, FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
@@ -5009,11 +5012,11 @@
       </c>
       <c r="D7" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>2553</v>
+        <v>1387</v>
       </c>
       <c r="E7" s="60">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
@@ -5025,11 +5028,11 @@
       </c>
       <c r="D8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>1855</v>
+        <v>796</v>
       </c>
       <c r="E8" s="60">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
@@ -5041,11 +5044,11 @@
       </c>
       <c r="D9" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>1231</v>
+        <v>2712</v>
       </c>
       <c r="E9" s="60">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
@@ -5057,7 +5060,7 @@
       </c>
       <c r="D10" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>560</v>
+        <v>3181</v>
       </c>
       <c r="E10" s="60">
         <f t="shared" ca="1" si="1"/>
@@ -5073,11 +5076,11 @@
       </c>
       <c r="D11" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>2607</v>
+        <v>1621</v>
       </c>
       <c r="E11" s="60">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
@@ -5089,11 +5092,11 @@
       </c>
       <c r="D12" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>855</v>
+        <v>2361</v>
       </c>
       <c r="E12" s="60">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5152,7 +5155,7 @@
       </c>
       <c r="D3" s="2">
         <f ca="1">RANDBETWEEN(250, 3200)</f>
-        <v>2901</v>
+        <v>1466</v>
       </c>
       <c r="E3" s="60">
         <f ca="1">RANDBETWEEN(0, 2)</f>
@@ -5163,7 +5166,7 @@
       </c>
       <c r="H3" s="2">
         <f ca="1">_xlfn.XLOOKUP(Table69[[#This Row],[Ticker]], Table18[Ticker], Table18[Price], "Missing")</f>
-        <v>2901</v>
+        <v>1466</v>
       </c>
       <c r="I3" s="2">
         <f ca="1">_xlfn.XLOOKUP(Table69[[#This Row],[Ticker]], Table18[Ticker], Table18[Dividend], "Missing")</f>
@@ -5179,22 +5182,22 @@
       </c>
       <c r="D4" s="2">
         <f t="shared" ref="D4:D12" ca="1" si="0">RANDBETWEEN(250, 3200)</f>
-        <v>1365</v>
+        <v>1030</v>
       </c>
       <c r="E4" s="60">
         <f t="shared" ref="E4:E12" ca="1" si="1">RANDBETWEEN(0, 2)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" t="s">
         <v>78</v>
       </c>
       <c r="H4" s="2">
         <f ca="1">_xlfn.XLOOKUP(Table69[[#This Row],[Ticker]], Table18[Ticker], Table18[Price], "Missing")</f>
-        <v>1365</v>
+        <v>1030</v>
       </c>
       <c r="I4" s="2">
         <f ca="1">_xlfn.XLOOKUP(Table69[[#This Row],[Ticker]], Table18[Ticker], Table18[Dividend], "Missing")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
@@ -5206,22 +5209,22 @@
       </c>
       <c r="D5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>1103</v>
+        <v>3033</v>
       </c>
       <c r="E5" s="60">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="s">
         <v>79</v>
       </c>
       <c r="H5" s="2">
         <f ca="1">_xlfn.XLOOKUP(Table69[[#This Row],[Ticker]], Table18[Ticker], Table18[Price], "Missing")</f>
-        <v>2542</v>
+        <v>769</v>
       </c>
       <c r="I5" s="2">
         <f ca="1">_xlfn.XLOOKUP(Table69[[#This Row],[Ticker]], Table18[Ticker], Table18[Dividend], "Missing")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
@@ -5233,18 +5236,18 @@
       </c>
       <c r="D6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>1537</v>
+        <v>333</v>
       </c>
       <c r="E6" s="60">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" t="s">
         <v>105</v>
       </c>
       <c r="H6" s="2">
         <f ca="1">_xlfn.XLOOKUP(Table69[[#This Row],[Ticker]], Table18[Ticker], Table18[Price], "Missing")</f>
-        <v>1787</v>
+        <v>625</v>
       </c>
       <c r="I6" s="2">
         <f ca="1">_xlfn.XLOOKUP(Table69[[#This Row],[Ticker]], Table18[Ticker], Table18[Dividend], "Missing")</f>
@@ -5260,11 +5263,11 @@
       </c>
       <c r="D7" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>1589</v>
+        <v>3181</v>
       </c>
       <c r="E7" s="60">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
@@ -5276,11 +5279,11 @@
       </c>
       <c r="D8" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>2542</v>
+        <v>769</v>
       </c>
       <c r="E8" s="60">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
@@ -5292,11 +5295,11 @@
       </c>
       <c r="D9" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>838</v>
+        <v>2455</v>
       </c>
       <c r="E9" s="60">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
@@ -5308,11 +5311,11 @@
       </c>
       <c r="D10" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>459</v>
+        <v>2949</v>
       </c>
       <c r="E10" s="60">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
@@ -5324,7 +5327,7 @@
       </c>
       <c r="D11" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>1787</v>
+        <v>625</v>
       </c>
       <c r="E11" s="60">
         <f t="shared" ca="1" si="1"/>
@@ -5340,7 +5343,7 @@
       </c>
       <c r="D12" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>1472</v>
+        <v>2842</v>
       </c>
       <c r="E12" s="60">
         <f t="shared" ca="1" si="1"/>
@@ -5408,15 +5411,15 @@
       </c>
       <c r="C3" s="62">
         <f ca="1">RANDBETWEEN(120, 150)</f>
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D3" s="62">
         <f ca="1">RANDBETWEEN(210, 260)</f>
-        <v>213</v>
+        <v>247</v>
       </c>
       <c r="E3" s="62">
         <f ca="1">RANDBETWEEN(330, 380)</f>
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="F3" s="62">
         <v>1250</v>
@@ -5440,7 +5443,7 @@
       </c>
       <c r="M3" s="62" cm="1">
         <f t="array" aca="1" ref="M3" ca="1">INDEX($C$3:$G$8, K3,L3)</f>
-        <v>349</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.3">
@@ -5449,15 +5452,15 @@
       </c>
       <c r="C4" s="62">
         <f t="shared" ref="C4:C8" ca="1" si="0">RANDBETWEEN(120, 150)</f>
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="D4" s="62">
         <f t="shared" ref="D4:D8" ca="1" si="1">RANDBETWEEN(210, 260)</f>
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="E4" s="62">
         <f t="shared" ref="E4:E8" ca="1" si="2">RANDBETWEEN(330, 380)</f>
-        <v>349</v>
+        <v>377</v>
       </c>
       <c r="F4" s="62">
         <v>1300</v>
@@ -5481,7 +5484,7 @@
       </c>
       <c r="M4" s="62" cm="1">
         <f t="array" aca="1" ref="M4" ca="1">INDEX($C$3:$G$8, K4,L4)</f>
-        <v>227</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.3">
@@ -5490,15 +5493,15 @@
       </c>
       <c r="C5" s="62">
         <f t="shared" ca="1" si="0"/>
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="D5" s="62">
         <f t="shared" ca="1" si="1"/>
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="E5" s="62">
         <f t="shared" ca="1" si="2"/>
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="F5" s="62">
         <v>1350</v>
@@ -5531,7 +5534,7 @@
       </c>
       <c r="C6" s="62">
         <f t="shared" ca="1" si="0"/>
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="D6" s="62">
         <f t="shared" ca="1" si="1"/>
@@ -5539,7 +5542,7 @@
       </c>
       <c r="E6" s="62">
         <f t="shared" ca="1" si="2"/>
-        <v>367</v>
+        <v>338</v>
       </c>
       <c r="F6" s="62">
         <v>1400</v>
@@ -5572,7 +5575,7 @@
       </c>
       <c r="C7" s="62">
         <f t="shared" ca="1" si="0"/>
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="D7" s="62">
         <f t="shared" ca="1" si="1"/>
@@ -5580,7 +5583,7 @@
       </c>
       <c r="E7" s="62">
         <f t="shared" ca="1" si="2"/>
-        <v>330</v>
+        <v>376</v>
       </c>
       <c r="F7" s="62">
         <v>1450</v>
@@ -5613,15 +5616,15 @@
       </c>
       <c r="C8" s="62">
         <f t="shared" ca="1" si="0"/>
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="D8" s="62">
         <f t="shared" ca="1" si="1"/>
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="E8" s="62">
         <f t="shared" ca="1" si="2"/>
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="F8" s="62">
         <v>1500</v>
@@ -5666,15 +5669,15 @@
       </c>
       <c r="C3">
         <f ca="1">RANDBETWEEN(5, 50)</f>
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D3" s="69">
         <f ca="1">RANDBETWEEN(1000, 100000)</f>
-        <v>77720</v>
+        <v>55923</v>
       </c>
       <c r="E3" s="75" cm="1">
         <f t="array" aca="1" ref="E3:E13" ca="1">C3:C13*D3:D13</f>
-        <v>3419680</v>
+        <v>2292843</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
@@ -5683,15 +5686,15 @@
       </c>
       <c r="C4">
         <f t="shared" ref="C4:C13" ca="1" si="0">RANDBETWEEN(5, 50)</f>
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D4" s="69">
         <f t="shared" ref="D4:D13" ca="1" si="1">RANDBETWEEN(1000, 100000)</f>
-        <v>49865</v>
+        <v>80905</v>
       </c>
       <c r="E4" s="76">
         <f ca="1"/>
-        <v>1396220</v>
+        <v>2508055</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
@@ -5700,15 +5703,15 @@
       </c>
       <c r="C5">
         <f t="shared" ca="1" si="0"/>
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="D5" s="69">
         <f t="shared" ca="1" si="1"/>
-        <v>18741</v>
+        <v>24565</v>
       </c>
       <c r="E5" s="76">
         <f ca="1"/>
-        <v>880827</v>
+        <v>122825</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
@@ -5717,15 +5720,15 @@
       </c>
       <c r="C6">
         <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D6" s="69">
         <f t="shared" ca="1" si="1"/>
-        <v>86323</v>
+        <v>23022</v>
       </c>
       <c r="E6" s="76">
         <f ca="1"/>
-        <v>949553</v>
+        <v>713682</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
@@ -5734,15 +5737,15 @@
       </c>
       <c r="C7">
         <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="D7" s="69">
         <f t="shared" ca="1" si="1"/>
-        <v>97775</v>
+        <v>81275</v>
       </c>
       <c r="E7" s="76">
         <f ca="1"/>
-        <v>1466625</v>
+        <v>3413550</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
@@ -5751,15 +5754,15 @@
       </c>
       <c r="C8">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D8" s="69">
         <f t="shared" ca="1" si="1"/>
-        <v>6004</v>
+        <v>19191</v>
       </c>
       <c r="E8" s="76">
         <f ca="1"/>
-        <v>108072</v>
+        <v>671685</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
@@ -5768,15 +5771,15 @@
       </c>
       <c r="C9">
         <f t="shared" ca="1" si="0"/>
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D9" s="69">
         <f t="shared" ca="1" si="1"/>
-        <v>87532</v>
+        <v>90218</v>
       </c>
       <c r="E9" s="76">
         <f ca="1"/>
-        <v>4289068</v>
+        <v>3247848</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
@@ -5785,15 +5788,15 @@
       </c>
       <c r="C10">
         <f t="shared" ca="1" si="0"/>
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D10" s="69">
         <f t="shared" ca="1" si="1"/>
-        <v>65568</v>
+        <v>24655</v>
       </c>
       <c r="E10" s="76">
         <f ca="1"/>
-        <v>3081696</v>
+        <v>714995</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
@@ -5802,15 +5805,15 @@
       </c>
       <c r="C11">
         <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D11" s="69">
         <f t="shared" ca="1" si="1"/>
-        <v>88406</v>
+        <v>10859</v>
       </c>
       <c r="E11" s="76">
         <f ca="1"/>
-        <v>3182616</v>
+        <v>206321</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
@@ -5819,15 +5822,15 @@
       </c>
       <c r="C12">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D12" s="69">
         <f t="shared" ca="1" si="1"/>
-        <v>82861</v>
+        <v>55412</v>
       </c>
       <c r="E12" s="76">
         <f ca="1"/>
-        <v>2320108</v>
+        <v>2105656</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
@@ -5836,15 +5839,15 @@
       </c>
       <c r="C13" s="71">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D13" s="72">
         <f t="shared" ca="1" si="1"/>
-        <v>71798</v>
+        <v>82278</v>
       </c>
       <c r="E13" s="77">
         <f ca="1"/>
-        <v>1364162</v>
+        <v>3702510</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
@@ -5855,7 +5858,7 @@
       <c r="D14" s="74"/>
       <c r="E14" s="78">
         <f ca="1">SUM(_xlfn.ANCHORARRAY(E3))</f>
-        <v>22458627</v>
+        <v>19699970</v>
       </c>
     </row>
   </sheetData>
@@ -5960,258 +5963,243 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
-      <c r="L1" s="80"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
+      <c r="L1" s="88"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="83" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="84"/>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84" t="s">
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84" t="s">
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="81">
+      <c r="A3" s="84">
         <v>46144</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="83">
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="86">
         <v>250.25</v>
       </c>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="82"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="85"/>
+      <c r="L3" s="85"/>
       <c r="N3" s="11" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="81">
+      <c r="A4" s="84">
         <v>46145</v>
       </c>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="83">
+      <c r="B4" s="85"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="86">
         <v>300</v>
       </c>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="79">
+      <c r="F4" s="86"/>
+      <c r="G4" s="86"/>
+      <c r="H4" s="86"/>
+      <c r="I4" s="87">
         <f>(E4-E3)/E3</f>
         <v>0.19880119880119881</v>
       </c>
-      <c r="J4" s="79"/>
-      <c r="K4" s="79"/>
-      <c r="L4" s="79"/>
+      <c r="J4" s="87"/>
+      <c r="K4" s="87"/>
+      <c r="L4" s="87"/>
       <c r="N4" s="10">
         <f>AVERAGE(I4:L11)</f>
         <v>-8.1596436336491718E-2</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="81">
+      <c r="A5" s="84">
         <v>46146</v>
       </c>
-      <c r="B5" s="82"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="83">
+      <c r="B5" s="85"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85"/>
+      <c r="E5" s="86">
         <v>350.15</v>
       </c>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="79">
+      <c r="F5" s="86"/>
+      <c r="G5" s="86"/>
+      <c r="H5" s="86"/>
+      <c r="I5" s="87">
         <f>(E5-E4)/E4</f>
         <v>0.1671666666666666</v>
       </c>
-      <c r="J5" s="79"/>
-      <c r="K5" s="79"/>
-      <c r="L5" s="79"/>
+      <c r="J5" s="87"/>
+      <c r="K5" s="87"/>
+      <c r="L5" s="87"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A6" s="81">
+      <c r="A6" s="84">
         <v>46147</v>
       </c>
-      <c r="B6" s="82"/>
-      <c r="C6" s="82"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="83">
+      <c r="B6" s="85"/>
+      <c r="C6" s="85"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="86">
         <v>650.5</v>
       </c>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="79">
+      <c r="F6" s="86"/>
+      <c r="G6" s="86"/>
+      <c r="H6" s="86"/>
+      <c r="I6" s="87">
         <f>(E6-E5)/E5</f>
         <v>0.85777523918320731</v>
       </c>
-      <c r="J6" s="79"/>
-      <c r="K6" s="79"/>
-      <c r="L6" s="79"/>
+      <c r="J6" s="87"/>
+      <c r="K6" s="87"/>
+      <c r="L6" s="87"/>
       <c r="N6" s="11" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A7" s="81">
+      <c r="A7" s="84">
         <v>46148</v>
       </c>
-      <c r="B7" s="82"/>
-      <c r="C7" s="82"/>
-      <c r="D7" s="82"/>
-      <c r="E7" s="83">
+      <c r="B7" s="85"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="86">
         <v>600.35</v>
       </c>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="79">
+      <c r="F7" s="86"/>
+      <c r="G7" s="86"/>
+      <c r="H7" s="86"/>
+      <c r="I7" s="87">
         <f t="shared" ref="I7:I10" si="0">(E7-E6)/E6</f>
         <v>-7.7094542659492657E-2</v>
       </c>
-      <c r="J7" s="79"/>
-      <c r="K7" s="79"/>
-      <c r="L7" s="79"/>
+      <c r="J7" s="87"/>
+      <c r="K7" s="87"/>
+      <c r="L7" s="87"/>
       <c r="N7" s="12" t="str">
         <f>IF(N4&gt;0,"Positive","Negative")</f>
         <v>Negative</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="81">
+      <c r="A8" s="84">
         <v>46149</v>
       </c>
-      <c r="B8" s="82"/>
-      <c r="C8" s="82"/>
-      <c r="D8" s="82"/>
-      <c r="E8" s="83">
+      <c r="B8" s="85"/>
+      <c r="C8" s="85"/>
+      <c r="D8" s="85"/>
+      <c r="E8" s="86">
         <v>150.19999999999999</v>
       </c>
-      <c r="F8" s="83"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="83"/>
-      <c r="I8" s="79">
+      <c r="F8" s="86"/>
+      <c r="G8" s="86"/>
+      <c r="H8" s="86"/>
+      <c r="I8" s="87">
         <f t="shared" si="0"/>
         <v>-0.74981260931123517</v>
       </c>
-      <c r="J8" s="79"/>
-      <c r="K8" s="79"/>
-      <c r="L8" s="79"/>
+      <c r="J8" s="87"/>
+      <c r="K8" s="87"/>
+      <c r="L8" s="87"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="81">
+      <c r="A9" s="84">
         <v>46150</v>
       </c>
-      <c r="B9" s="82"/>
-      <c r="C9" s="82"/>
-      <c r="D9" s="82"/>
-      <c r="E9" s="83">
+      <c r="B9" s="85"/>
+      <c r="C9" s="85"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="86">
         <v>55.5</v>
       </c>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="79">
+      <c r="F9" s="86"/>
+      <c r="G9" s="86"/>
+      <c r="H9" s="86"/>
+      <c r="I9" s="87">
         <f t="shared" si="0"/>
         <v>-0.6304926764314247</v>
       </c>
-      <c r="J9" s="79"/>
-      <c r="K9" s="79"/>
-      <c r="L9" s="79"/>
+      <c r="J9" s="87"/>
+      <c r="K9" s="87"/>
+      <c r="L9" s="87"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="81">
+      <c r="A10" s="84">
         <v>46151</v>
       </c>
-      <c r="B10" s="82"/>
-      <c r="C10" s="82"/>
-      <c r="D10" s="82"/>
-      <c r="E10" s="83">
+      <c r="B10" s="85"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="86">
         <v>80.5</v>
       </c>
-      <c r="F10" s="83"/>
-      <c r="G10" s="83"/>
-      <c r="H10" s="83"/>
-      <c r="I10" s="79">
+      <c r="F10" s="86"/>
+      <c r="G10" s="86"/>
+      <c r="H10" s="86"/>
+      <c r="I10" s="87">
         <f t="shared" si="0"/>
         <v>0.45045045045045046</v>
       </c>
-      <c r="J10" s="79"/>
-      <c r="K10" s="79"/>
-      <c r="L10" s="79"/>
+      <c r="J10" s="87"/>
+      <c r="K10" s="87"/>
+      <c r="L10" s="87"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="81">
+      <c r="A11" s="84">
         <v>46152</v>
       </c>
-      <c r="B11" s="82"/>
-      <c r="C11" s="82"/>
-      <c r="D11" s="82"/>
-      <c r="E11" s="83">
+      <c r="B11" s="85"/>
+      <c r="C11" s="85"/>
+      <c r="D11" s="85"/>
+      <c r="E11" s="86">
         <v>10.5</v>
       </c>
-      <c r="F11" s="83"/>
-      <c r="G11" s="83"/>
-      <c r="H11" s="83"/>
-      <c r="I11" s="79">
+      <c r="F11" s="86"/>
+      <c r="G11" s="86"/>
+      <c r="H11" s="86"/>
+      <c r="I11" s="87">
         <f t="shared" ref="I11" si="1">(E11-E10)/E10</f>
         <v>-0.86956521739130432</v>
       </c>
-      <c r="J11" s="79"/>
-      <c r="K11" s="79"/>
-      <c r="L11" s="79"/>
+      <c r="J11" s="87"/>
+      <c r="K11" s="87"/>
+      <c r="L11" s="87"/>
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="E5:H5"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="E8:H8"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A7:D7"/>
     <mergeCell ref="I10:L10"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A11:D11"/>
@@ -6228,6 +6216,21 @@
     <mergeCell ref="I9:L9"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="E4:H4"/>
+    <mergeCell ref="E5:H5"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="E8:H8"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A5:D5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6508,27 +6511,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="85" t="s">
+      <c r="B1" s="89" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="86" t="s">
+      <c r="C1" s="90" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86" t="s">
+      <c r="D1" s="90"/>
+      <c r="E1" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="86"/>
-      <c r="G1" s="85" t="s">
+      <c r="F1" s="90"/>
+      <c r="G1" s="89" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="85"/>
-      <c r="B2" s="85"/>
+      <c r="A2" s="89"/>
+      <c r="B2" s="89"/>
       <c r="C2" s="21" t="s">
         <v>33</v>
       </c>
@@ -6541,167 +6544,167 @@
       <c r="F2" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="G2" s="85"/>
+      <c r="G2" s="89"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="81" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="93">
+      <c r="B3" s="82">
         <f ca="1">RANDBETWEEN(10, 50)</f>
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C3" s="12">
         <f ca="1">RANDBETWEEN(2, 10)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="12">
         <f ca="1">RANDBETWEEN(2, 10)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3" s="22">
         <f ca="1">$B3*C3</f>
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="F3" s="25">
         <f ca="1">$B3*D3</f>
-        <v>91</v>
+        <v>126</v>
       </c>
       <c r="G3" s="28">
         <f ca="1">(E3+F3)/(E$8+F$8)</f>
-        <v>0.13763233878729547</v>
+        <v>0.21730950141110067</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="92" t="s">
+      <c r="A4" s="81" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="93">
+      <c r="B4" s="82">
         <f t="shared" ref="B4:B7" ca="1" si="0">RANDBETWEEN(10, 50)</f>
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C4" s="12">
         <f t="shared" ref="C4:D7" ca="1" si="1">RANDBETWEEN(2, 10)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D4" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E4" s="22">
         <f t="shared" ref="E4:F7" ca="1" si="2">$B4*C4</f>
-        <v>81</v>
+        <v>128</v>
       </c>
       <c r="F4" s="26">
         <f t="shared" ca="1" si="2"/>
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="G4" s="28">
         <f ca="1">(E4+F4)/(E$8+F$8)</f>
-        <v>0.12993262752646775</v>
+        <v>0.22577610536218251</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="81" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="93">
+      <c r="B5" s="82">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C5" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D5" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E5" s="22">
         <f t="shared" ca="1" si="2"/>
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="F5" s="25">
         <f t="shared" ca="1" si="2"/>
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="G5" s="28">
         <f t="shared" ref="G5:G7" ca="1" si="3">(E5+F5)/(E$8+F$8)</f>
-        <v>0.23291626564003851</v>
+        <v>0.28222013170272814</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="92" t="s">
+      <c r="A6" s="81" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="93">
+      <c r="B6" s="82">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E6" s="22">
         <f t="shared" ca="1" si="2"/>
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="F6" s="25">
         <f t="shared" ca="1" si="2"/>
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G6" s="28">
         <f t="shared" ca="1" si="3"/>
-        <v>0.23676612127045235</v>
+        <v>9.4073377234242708E-2</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="92" t="s">
+      <c r="A7" s="81" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="93">
+      <c r="B7" s="82">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D7" s="12">
         <f t="shared" ca="1" si="1"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E7" s="22">
         <f t="shared" ca="1" si="2"/>
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="F7" s="25">
         <f t="shared" ca="1" si="2"/>
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G7" s="28">
         <f t="shared" ca="1" si="3"/>
-        <v>0.26275264677574589</v>
+        <v>0.18062088428974601</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="90" t="s">
+      <c r="A8" s="79" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="91"/>
-      <c r="C8" s="91"/>
-      <c r="D8" s="91"/>
+      <c r="B8" s="80"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="80"/>
       <c r="E8" s="27">
         <f ca="1">SUM(E3:E7)</f>
-        <v>576</v>
+        <v>377</v>
       </c>
       <c r="F8" s="27">
         <f ca="1">SUM(F3:F7)</f>
-        <v>463</v>
+        <v>686</v>
       </c>
       <c r="G8" s="24"/>
     </row>
@@ -6739,10 +6742,10 @@
       <c r="C1" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="F1" s="87" t="s">
+      <c r="F1" s="91" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="87"/>
+      <c r="G1" s="91"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="41" t="s">
@@ -6753,14 +6756,14 @@
       </c>
       <c r="C2" s="31">
         <f ca="1">RANDBETWEEN(500, 1000)</f>
-        <v>761</v>
+        <v>635</v>
       </c>
       <c r="F2" s="35" t="s">
         <v>48</v>
       </c>
       <c r="G2" s="36">
         <f ca="1">SUMIF($A$2:$A$9, F2, $C$2:$C$9)</f>
-        <v>1363</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -6772,14 +6775,14 @@
       </c>
       <c r="C3" s="34">
         <f t="shared" ref="C3:C9" ca="1" si="0">RANDBETWEEN(500, 1000)</f>
-        <v>738</v>
+        <v>544</v>
       </c>
       <c r="F3" s="24" t="s">
         <v>50</v>
       </c>
       <c r="G3" s="24">
         <f ca="1">SUMIFS($C$2:$C$9, $A$2:$A$9, F2, $B$2:$B$9, F3)</f>
-        <v>853</v>
+        <v>514</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -6791,14 +6794,14 @@
       </c>
       <c r="C4" s="34">
         <f t="shared" ca="1" si="0"/>
-        <v>869</v>
+        <v>749</v>
       </c>
       <c r="F4" s="24" t="s">
         <v>51</v>
       </c>
       <c r="G4" s="24">
         <f ca="1">SUMIFS($C$2:$C$9, $A$2:$A$9, F2, $B$2:$B$9, F4)</f>
-        <v>510</v>
+        <v>754</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -6810,14 +6813,14 @@
       </c>
       <c r="C5" s="34">
         <f t="shared" ca="1" si="0"/>
-        <v>795</v>
+        <v>914</v>
       </c>
       <c r="F5" s="35" t="s">
         <v>46</v>
       </c>
       <c r="G5" s="36">
         <f ca="1">SUMIF($A$2:$A$9, F5, $C$2:$C$9)</f>
-        <v>1499</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -6829,14 +6832,14 @@
       </c>
       <c r="C6" s="34">
         <f t="shared" ca="1" si="0"/>
-        <v>853</v>
+        <v>514</v>
       </c>
       <c r="F6" s="24" t="s">
         <v>50</v>
       </c>
       <c r="G6" s="24">
         <f ca="1">SUMIFS($C$2:$C$9, $A$2:$A$9, F5, $B$2:$B$9, F6)</f>
-        <v>761</v>
+        <v>635</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -6848,14 +6851,14 @@
       </c>
       <c r="C7" s="34">
         <f t="shared" ca="1" si="0"/>
-        <v>510</v>
+        <v>754</v>
       </c>
       <c r="F7" s="24" t="s">
         <v>51</v>
       </c>
       <c r="G7" s="24">
         <f ca="1">SUMIFS($C$2:$C$9, $A$2:$A$9, F5, $B$2:$B$9, F7)</f>
-        <v>738</v>
+        <v>544</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -6867,14 +6870,14 @@
       </c>
       <c r="C8" s="34">
         <f t="shared" ca="1" si="0"/>
-        <v>885</v>
+        <v>682</v>
       </c>
       <c r="F8" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G8" s="36">
         <f ca="1">SUMIF($A$2:$A$9, F8, $C$2:$C$9)</f>
-        <v>1664</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -6886,14 +6889,14 @@
       </c>
       <c r="C9" s="32">
         <f t="shared" ca="1" si="0"/>
-        <v>598</v>
+        <v>628</v>
       </c>
       <c r="F9" s="24" t="s">
         <v>50</v>
       </c>
       <c r="G9" s="24">
         <f ca="1">SUMIFS($C$2:$C$9, $A$2:$A$9, F8, $B$2:$B$9, F9)</f>
-        <v>869</v>
+        <v>749</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -6902,7 +6905,7 @@
       </c>
       <c r="G10" s="24">
         <f ca="1">SUMIFS($C$2:$C$9, $A$2:$A$9, F8, $B$2:$B$9, F10)</f>
-        <v>795</v>
+        <v>914</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -6911,7 +6914,7 @@
       </c>
       <c r="G11" s="36">
         <f ca="1">SUMIF($A$2:$A$9, F11, $C$2:$C$9)</f>
-        <v>1483</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -6920,7 +6923,7 @@
       </c>
       <c r="G12" s="24">
         <f ca="1">SUMIFS($C$2:$C$9, $A$2:$A$9, F11, $B$2:$B$9, F12)</f>
-        <v>885</v>
+        <v>682</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -6929,7 +6932,7 @@
       </c>
       <c r="G13" s="24">
         <f ca="1">SUMIFS($C$2:$C$9, $A$2:$A$9, F11, $B$2:$B$9, F13)</f>
-        <v>598</v>
+        <v>628</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -6938,7 +6941,7 @@
       </c>
       <c r="G14" s="33">
         <f ca="1">SUM(G2,G5,G8,G11)</f>
-        <v>6009</v>
+        <v>5420</v>
       </c>
     </row>
   </sheetData>
@@ -6980,74 +6983,74 @@
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B2" s="50" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C2" s="50" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D2" s="50" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E2" s="51">
-        <v>60000</v>
+        <v>7000</v>
       </c>
       <c r="F2" s="52">
-        <f>DATE(2026, 10, 5)</f>
-        <v>46300</v>
+        <f>DATE(2026, 5, 7)</f>
+        <v>46149</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B3" s="50" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C3" s="50" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D3" s="50" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E3" s="51">
-        <v>50000</v>
+        <v>6000</v>
       </c>
       <c r="F3" s="52">
-        <f>DATE(2026, 4, 7)</f>
-        <v>46119</v>
+        <f>DATE(2026, 6, 6)</f>
+        <v>46179</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B4" s="50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C4" s="50" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D4" s="50" t="s">
         <v>67</v>
       </c>
       <c r="E4" s="51">
+        <v>7500</v>
+      </c>
+      <c r="F4" s="52">
+        <f>DATE(2026, 5, 7)</f>
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="50" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="51">
         <v>25000</v>
       </c>
-      <c r="F4" s="52">
+      <c r="F5" s="52">
         <f>DATE(2026, 8, 7)</f>
         <v>46241</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="50" t="s">
-        <v>65</v>
-      </c>
-      <c r="C5" s="50" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" s="50" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" s="51">
-        <v>15000</v>
-      </c>
-      <c r="F5" s="52">
-        <f>DATE(2026, 5, 8)</f>
-        <v>46150</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
@@ -7070,63 +7073,63 @@
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="50" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D7" s="50" t="s">
         <v>67</v>
       </c>
       <c r="E7" s="51">
-        <v>7500</v>
+        <v>60000</v>
       </c>
       <c r="F7" s="52">
-        <f>DATE(2026, 5, 7)</f>
-        <v>46149</v>
+        <f>DATE(2026, 10, 5)</f>
+        <v>46300</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="50" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C8" s="50" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="D8" s="50" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E8" s="51">
-        <v>7000</v>
+        <v>50000</v>
       </c>
       <c r="F8" s="52">
-        <f>DATE(2026, 5, 7)</f>
-        <v>46149</v>
+        <f>DATE(2026, 4, 7)</f>
+        <v>46119</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="53" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C9" s="53" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D9" s="53" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E9" s="54">
-        <v>6000</v>
+        <v>15000</v>
       </c>
       <c r="F9" s="55">
-        <f>DATE(2026, 6, 6)</f>
-        <v>46179</v>
+        <f>DATE(2026, 5, 8)</f>
+        <v>46150</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C12" s="88" t="s">
+      <c r="C12" s="92" t="s">
         <v>74</v>
       </c>
-      <c r="D12" s="88"/>
+      <c r="D12" s="92"/>
       <c r="E12" s="56">
         <f>SUM(JLoka_Investors[INVESTMENT AMOUNT (USD)])</f>
         <v>180500</v>
@@ -7165,12 +7168,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="B2" s="89" t="s">
+      <c r="B2" s="93" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
       <c r="F2" s="57"/>
     </row>
     <row r="3" spans="2:6" s="57" customFormat="1" x14ac:dyDescent="0.3">
@@ -7193,15 +7196,15 @@
       </c>
       <c r="C4" s="3">
         <f ca="1">RAND()</f>
-        <v>0.11080121388456066</v>
+        <v>0.20059331458471186</v>
       </c>
       <c r="D4" s="3">
         <f t="shared" ref="D4:E4" ca="1" si="0">RAND()</f>
-        <v>0.88566478997338571</v>
+        <v>0.1002504986995838</v>
       </c>
       <c r="E4" s="3">
         <f t="shared" ca="1" si="0"/>
-        <v>0.97117624755734233</v>
+        <v>0.19382124045866378</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.3">
@@ -7210,15 +7213,15 @@
       </c>
       <c r="C5" s="3">
         <f t="shared" ref="C5:E14" ca="1" si="1">RAND()</f>
-        <v>0.53966467512723337</v>
+        <v>0.94441785918024312</v>
       </c>
       <c r="D5" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.73072885920293484</v>
+        <v>0.21260315046420197</v>
       </c>
       <c r="E5" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.87907102792245906</v>
+        <v>0.42167031427975654</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.3">
@@ -7227,15 +7230,15 @@
       </c>
       <c r="C6" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.22518088577689821</v>
+        <v>8.6915784118192341E-2</v>
       </c>
       <c r="D6" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.22356504089203866</v>
+        <v>0.995673661150418</v>
       </c>
       <c r="E6" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.55144837190485618</v>
+        <v>0.52662624457069562</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.3">
@@ -7244,15 +7247,15 @@
       </c>
       <c r="C7" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>4.6615126018486275E-2</v>
+        <v>0.11100161243085194</v>
       </c>
       <c r="D7" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.91547741076720424</v>
+        <v>0.73304382628663689</v>
       </c>
       <c r="E7" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.26848087893021488</v>
+        <v>0.85318437891805488</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.3">
@@ -7261,15 +7264,15 @@
       </c>
       <c r="C8" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.8702354955083681</v>
+        <v>0.66699718988218426</v>
       </c>
       <c r="D8" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>1.5247083874135092E-2</v>
+        <v>0.97227422532088059</v>
       </c>
       <c r="E8" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.22986145590904394</v>
+        <v>0.32314197933022382</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.3">
@@ -7278,15 +7281,15 @@
       </c>
       <c r="C9" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>3.0926012166387684E-2</v>
+        <v>0.24966708871427501</v>
       </c>
       <c r="D9" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.57932526750454472</v>
+        <v>0.94142684597969861</v>
       </c>
       <c r="E9" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.2486301162043244</v>
+        <v>0.32787160268776661</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.3">
@@ -7295,15 +7298,15 @@
       </c>
       <c r="C10" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>8.8551138159630782E-2</v>
+        <v>0.87754600403962557</v>
       </c>
       <c r="D10" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.22884202106672469</v>
+        <v>0.21421877494508046</v>
       </c>
       <c r="E10" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.84990396601828477</v>
+        <v>0.83752860892351155</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.3">
@@ -7312,15 +7315,15 @@
       </c>
       <c r="C11" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.65332271221650706</v>
+        <v>0.73911835572370288</v>
       </c>
       <c r="D11" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>7.4932411321734005E-2</v>
+        <v>0.60395122269160229</v>
       </c>
       <c r="E11" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>3.5123198633126851E-3</v>
+        <v>0.48903074525455303</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.3">
@@ -7329,15 +7332,15 @@
       </c>
       <c r="C12" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.79215614449270955</v>
+        <v>0.85505503648803938</v>
       </c>
       <c r="D12" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.15459971516135507</v>
+        <v>9.4180672280433919E-3</v>
       </c>
       <c r="E12" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>9.3087121970948261E-2</v>
+        <v>0.77870766035609584</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.3">
@@ -7346,15 +7349,15 @@
       </c>
       <c r="C13" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.26667953215936857</v>
+        <v>0.91854943503885156</v>
       </c>
       <c r="D13" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.28533575202753148</v>
+        <v>0.49813295330831853</v>
       </c>
       <c r="E13" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.37420685227850292</v>
+        <v>0.4116528241380023</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.3">
@@ -7363,15 +7366,15 @@
       </c>
       <c r="C14" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.99577635299164857</v>
+        <v>0.53303090978041279</v>
       </c>
       <c r="D14" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>5.9259036510320717E-3</v>
+        <v>0.65868576205753238</v>
       </c>
       <c r="E14" s="3">
         <f t="shared" ca="1" si="1"/>
-        <v>0.96217109063538808</v>
+        <v>0.64940899731822843</v>
       </c>
     </row>
   </sheetData>
